--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260825.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260825.xlsx
@@ -931,17 +931,17 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>167,000</t>
+          <t>5,385,520</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -953,17 +953,17 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>5,385,520</t>
+          <t>167,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -1041,17 +1041,17 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>871,349</t>
+          <t>102,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1063,17 +1063,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>102,000</t>
+          <t>871,349</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>140,921</t>
+          <t>821,897</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1195,17 +1195,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>821,897</t>
+          <t>140,921</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>202609WTEU6F</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>電子指數期貨</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>2,036,587</t>
+          <t>42</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>202609WTEU6F</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>電子指數期貨</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>2,036,587</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>1,863,000</t>
+          <t>5,816,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>5,816,000</t>
+          <t>1,863,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>1,216,441</t>
+          <t>952,659</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>952,659</t>
+          <t>1,216,441</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>4,527,578</t>
+          <t>2,640,703</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>2,640,703</t>
+          <t>4,527,578</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>2409</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>友達</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>1,401,384</t>
+          <t>10,776,121</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>592,000</t>
+          <t>1,401,384</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2409</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>友達</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>10,776,121</t>
+          <t>592,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1679,17 +1679,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>202609WVHFU6F</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>富邦科技ETF期貨</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>1,205,076</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>202609WVHFU6F</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>富邦科技ETF期貨</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>1,205,076</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1767,17 +1767,17 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>5,042,956</t>
+          <t>789,000</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -1789,17 +1789,17 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>818,000</t>
+          <t>295,000</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -1811,17 +1811,17 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>宏碁</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>789,000</t>
+          <t>5,042,956</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -1833,17 +1833,17 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>295,000</t>
+          <t>818,000</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -1877,17 +1877,17 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>神達</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>1,586,400</t>
+          <t>325,000</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -1899,17 +1899,17 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>神達</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>325,000</t>
+          <t>1,586,400</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -1943,17 +1943,17 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>鴻準</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>1,019,121</t>
+          <t>1,787,000</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -1965,17 +1965,17 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>鴻準</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>1,787,000</t>
+          <t>1,019,121</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -2009,17 +2009,17 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>337,000</t>
+          <t>66,538</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -2031,17 +2031,17 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>66,538</t>
+          <t>337,000</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -2053,17 +2053,17 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>173,000</t>
+          <t>159,000</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -2075,17 +2075,17 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>181,000</t>
+          <t>691,000</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -2119,17 +2119,17 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>691,000</t>
+          <t>173,000</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -2141,17 +2141,17 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>159,000</t>
+          <t>181,000</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -2163,17 +2163,17 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>6526</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>台勝科</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>116,000</t>
+          <t>73,000</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
@@ -2185,17 +2185,17 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>6526</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>台勝科</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>73,000</t>
+          <t>116,000</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
